--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_776_Tonga.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_776_Tonga.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R8f7b7ec3b36e4a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R7b5307adb41045db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R58af3cd7215c4489"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5f387ab840b54427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R29b325776a2c4779"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R884e58db4cee4fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re8df41cc63864708"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9acf7cbc42634ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Redd3ac2f78e3453d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R261ff52693ef4349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R51d1d7b8b0334cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf445896605c24ff9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ776CommercialTable" displayName="EEZ776CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ776CommercialTable" displayName="EEZ776CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ776FunctionalTable" displayName="EEZ776FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ776FunctionalTable" displayName="EEZ776FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ776ValidationTable" displayName="EEZ776ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ776ValidationTable" displayName="EEZ776ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6456,7 +6410,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R645fdb54d8da4275"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d8004010d874d66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6466,20 +6420,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6487,498 +6431,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>54.16481898319999</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>54.16481898319999</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$87,A2,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>11059.036618415586</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>11059.036618415586</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>296.4546671654</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>50.11872336272725</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>296.4546671654</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$87,A3,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>14857.929453252063</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>14857.929453252063</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>57.68201502120001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.132235772357651</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>135.59253253369278</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>57.68201502120001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>135.84251709732632</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$87,A4,'Species'!$U$2:$U$87))</x:f>
-        <x:v>7835.670111725596</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.132235772357651</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>135.59253253369278</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>7821.250498371018</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>14.41961335457836</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0018436455088073</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0018436455088072714</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1180.8186686616</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1180.8186686616</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$87,A5,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>14865.626286990453</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>14865.626286990453</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1405.9853789455</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.3089073736221066</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>203.66076634607495</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1405.9853789455</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>213.15974366498273</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$87,A6,'Species'!$U$2:$U$87))</x:f>
-        <x:v>299699.4829727364</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.3089073736221066</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>203.66076634607495</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>286344.05974741717</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>13355.423225319246</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0466411743868547</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.04664117438685477</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3802.2921572958003</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.8214816756548244</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>66.29513749318367</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3802.2921572958003</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>322.5464690926825</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$87,A7,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1226415.909794559</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.8214816756548244</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>66.29513749318367</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>252073.48135717906</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>974342.4284373799</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>4.865311111630865</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>3.8653111116308647</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4178.4353196673</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.187732759839423</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1540.7520698644632</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4178.4353196673</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1663.1026594395355</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$87,A8,'Species'!$U$2:$U$87))</x:f>
-        <x:v>6949166.892434772</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.187732759839423</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1540.7520698644632</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>6437932.867572173</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>511234.02486259956</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0794096545239982</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.07940965452399824</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3566.5791749934006</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.37007437032324</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2344.630284807313</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3566.5791749934006</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2381.2504236944187</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$87,A9,'Species'!$U$2:$U$87))</x:f>
-        <x:v>8492918.171592725</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.37007437032324</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2344.630284807313</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>8362309.546852607</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>130608.62474011816</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0156187263827463</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.01561872638274631</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d7292ab69334a6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd471b29348c7424c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6988,20 +6608,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7009,930 +6619,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>40.704</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.42</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2630.2679918953813</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>40.704</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$87,A2,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>107062.4283421096</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.42</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>107062.4283421096</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.13262071150000002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.14</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>13.803842646028853</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.13262071150000002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>13.803842646028853</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$87,A3,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1.8306754331503894</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.14</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>13.803842646028853</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>1.8306754331503894</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>9.712</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.49</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>3090.295432513592</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>9.712</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$87,A4,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>30012.949240572005</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.49</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>30012.949240572005</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3625.482079472901</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.370508086362442</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2346.9729618309784</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3625.482079472901</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2383.22244027244</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$87,A5,'Species'!$U$2:$U$87))</x:f>
-        <x:v>8640330.248605408</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.370508086362442</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2346.9729618309784</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>8508908.41412565</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>131421.83447975852</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.015445204964433</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.01544520496443292</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1.641358151</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.7200000000000006</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>524.8074602497734</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1.641358151</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$87,A6,'Species'!$U$2:$U$87))</x:f>
-        <x:v>861.3970025865731</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.7200000000000006</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>524.8074602497734</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>861.397002586574</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>-9.094947017729282e-13</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>-1.0558368546000603e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>20.196780143399998</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.416283061974979</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>260.7852727542849</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>20.196780143399998</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>701.8570865030788</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$87,A7,'Species'!$U$2:$U$87))</x:f>
-        <x:v>14175.253268189957</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.416283061974979</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>260.7852727542849</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>5267.022818454894</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>8908.230449735063</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>2.691321787808076</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>1.6913217878080762</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4176.793961516301</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.1879165651659305</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1541.4042963748082</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4176.793961516301</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1663.5499762381726</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$87,A8,'Species'!$U$2:$U$87))</x:f>
-        <x:v>6948305.495432186</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.1879165651659305</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1541.4042963748082</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>6438128.157353582</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>510177.3380786041</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0792431162613443</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.07924311626134428</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1209.7440775285</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.3560552697535284</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>227.01537407815033</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1209.7440775285</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>271.9822118186272</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$87,A9,'Species'!$U$2:$U$87))</x:f>
-        <x:v>329028.8699406862</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.3560552697535284</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>227.01537407815033</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>274630.50429895933</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>54398.36564172688</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1980783809161617</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.1980783809161618</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>266.1656307955</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7014104048851233</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>502.81752370563197</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>266.1656307955</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>796.723558591625</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$87,A10,'Species'!$U$2:$U$87))</x:f>
-        <x:v>212060.4285421754</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7014104048851233</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>502.81752370563197</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>133832.74337214083</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>78227.68517003456</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.584518281542742</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.584518281542742</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2539.1975770596</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.8359424947777905</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>68.53974665080074</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2539.1975770596</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>225.8654796923798</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$87,A11,'Species'!$U$2:$U$87))</x:f>
-        <x:v>573517.0787762951</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.8359424947777905</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>68.53974665080074</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>174035.95862799208</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>399481.120148303</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>3.2953941432425915</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>2.2953941432425915</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1180.8186686616</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1180.8186686616</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$87,A12,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>14865.626286990453</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>14865.626286990453</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>296.4546671654</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>50.11872336272725</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>296.4546671654</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$87,A13,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>14857.929453252063</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>14857.929453252063</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>75.6877051428</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.27</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>186.20871366628674</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>75.6877051428</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>186.20871366628674</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$87,A14,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>14093.710214993984</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.27</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>186.20871366628674</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>14093.710214993984</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>289.9347515568</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.276211067702849</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>18.88909138438918</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>289.9347515568</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>23.5709491721594</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$87,A15,'Species'!$U$2:$U$87))</x:f>
-        <x:v>6834.037292187996</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.276211067702849</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>18.88909138438918</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>5476.604017666567</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1357.4332745214288</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2478604022022746</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.24786040220227468</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>105.2814014003</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.522427616925902</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>332.98725930064586</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>105.2814014003</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>588.7333091651716</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$87,A16,'Species'!$U$2:$U$87))</x:f>
-        <x:v>61982.667839945345</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.522427616925902</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>332.98725930064586</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>35057.365307617074</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>26925.30253232827</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.7680355410644075</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.7680355410644076</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>704.4649214277999</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.36218622339218</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>23.024288762364677</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>704.4649214277999</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>69.31327148724614</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$87,A17,'Species'!$U$2:$U$87))</x:f>
-        <x:v>48828.76835216662</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.36218622339218</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>23.024288762364677</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>16219.80377391021</x:v>
       </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>32608.96457825641</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>3.0104413735700306</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>2.010441373570031</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbbc1bfbdeee46ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc80372a76c01472a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8107,7 +7113,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8206,7 +7212,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>17016818.719265178</x:v>
+        <x:v>15387263.798386406</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8220,7 +7226,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>17016818.719265178</x:v>
+        <x:v>15773312.444911908</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8234,7 +7240,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1629554.9208787717</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8248,7 +7254,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1243506.2743532695</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8259,9 +7265,9 @@
         <x:v>EEZ_776</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8273,47 +7279,19 @@
         <x:v>EEZ_776</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_776</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_776</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd65e11316d1c42b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d878026db2a4818"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8360,7 +7338,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
